--- a/data/trans_orig/SE_ADU-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2007</t>
+          <t>Sexo adulto elegido en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,47 +768,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>686455</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>688351</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>688351</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>651860</t>
+          <t>654258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>726336</t>
+          <t>726255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,82 +846,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>692064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>694012</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>694012</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656027</t>
+          <t>656108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730503</t>
+          <t>728105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>966347</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>968393</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>968393</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>922591</t>
+          <t>923443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1013261</t>
+          <t>1015366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -1189,82 +1189,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>961800</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>961800</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916932</t>
+          <t>914827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1007602</t>
+          <t>1006750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>681957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>683841</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648026</t>
+          <t>646587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722375</t>
+          <t>721453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -1532,82 +1532,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676480</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>678509</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>678509</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639975</t>
+          <t>640897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714324</t>
+          <t>715763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,47 +1797,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1036614</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>1038612</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1038612</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>991528</t>
+          <t>994046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1083622</t>
+          <t>1085351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -1875,82 +1875,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>940404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>942222</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>942222</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>897212</t>
+          <t>895483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>989306</t>
+          <t>986788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,47 +2140,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3377229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>3379197</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3299203</t>
+          <t>3299502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3468302</t>
+          <t>3461675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3274586</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3276543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3187439</t>
+          <t>3194066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3356538</t>
+          <t>3356239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2012</t>
+          <t>Sexo adulto elegido en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,47 +2715,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>694994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>697050</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>697050</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658495</t>
+          <t>657282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>734842</t>
+          <t>739166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,78%</t>
         </is>
       </c>
     </row>
@@ -2793,82 +2793,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>703469</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>703469</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>665677</t>
+          <t>661353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742024</t>
+          <t>743237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,47 +3058,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1030078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>1032184</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1032184</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>987117</t>
+          <t>989133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1075894</t>
+          <t>1083532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3136,82 +3136,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015861</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>1017947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1017947</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>974237</t>
+          <t>966599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1063014</t>
+          <t>1060998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,47 +3401,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>775060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>777174</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>777174</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>732074</t>
+          <t>733424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>822338</t>
+          <t>814803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -3479,82 +3479,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>755515</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>757623</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>757623</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>712459</t>
+          <t>719994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>802723</t>
+          <t>801373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,47 +3744,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1049889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>1051901</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1051901</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1004752</t>
+          <t>1010904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1094382</t>
+          <t>1099632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -3822,82 +3822,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>945741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>947739</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>947739</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>905258</t>
+          <t>900008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>994888</t>
+          <t>988736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,47 +4087,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3556237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>3558309</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3558309</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3462499</t>
+          <t>3473059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3637809</t>
+          <t>3648696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -4165,82 +4165,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3424729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>3426779</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3426779</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3347279</t>
+          <t>3336392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3522589</t>
+          <t>3512029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2016</t>
+          <t>Sexo adulto elegido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,47 +4662,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>670902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>672839</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>672839</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>636290</t>
+          <t>636149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708701</t>
+          <t>709472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -4740,82 +4740,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>674800</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>674800</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>638938</t>
+          <t>638167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711349</t>
+          <t>711490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,47 +5005,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1040865</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>1042913</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1042913</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>997194</t>
+          <t>998409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1091997</t>
+          <t>1089587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -5083,82 +5083,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1020369</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>1022431</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1022431</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>975757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1068150</t>
+          <t>1066935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,47 +5348,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>782966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>785011</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>785011</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>742393</t>
+          <t>742476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>821596</t>
+          <t>824479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -5426,82 +5426,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>757460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>759552</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>759552</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722967</t>
+          <t>720084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>802170</t>
+          <t>802087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,47 +5691,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1041691</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>1043779</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1043779</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>999000</t>
+          <t>999795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1089016</t>
+          <t>1088710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -5769,82 +5769,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>937567</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>937567</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>892330</t>
+          <t>892636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>982346</t>
+          <t>981551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,47 +6034,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3542503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>3544542</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3466598</t>
+          <t>3459508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3630980</t>
+          <t>3628134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -6112,82 +6112,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3392333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>3394350</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3307912</t>
+          <t>3310758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3472294</t>
+          <t>3479384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2023</t>
+          <t>Sexo adulto elegido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>724208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>682734</t>
+          <t>681343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>805348</t>
+          <t>811367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -6687,82 +6687,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>633772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>635441</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>635441</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555424</t>
+          <t>549405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>678038</t>
+          <t>679429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>957438</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663876</t>
+          <t>649535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1095130</t>
+          <t>1097923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -7030,82 +7030,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1190490</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>1192864</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1192864</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1056386</t>
+          <t>1053593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1487640</t>
+          <t>1501981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,47 +7295,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>931656</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>933366</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>933366</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>818667</t>
+          <t>814492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1156849</t>
+          <t>1156841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7373,82 +7373,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>702681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>704680</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>704680</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>481197</t>
+          <t>481205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819379</t>
+          <t>823554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,47 +7638,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1093587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>1094932</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1094932</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1039408</t>
+          <t>1039486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1207860</t>
+          <t>1207217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -7716,82 +7716,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>926831</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>926831</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813903</t>
+          <t>814546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>982355</t>
+          <t>982277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,47 +7981,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3710952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>3712280</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3712280</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3347397</t>
+          <t>3360210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4010183</t>
+          <t>3998706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -8059,82 +8059,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3457849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>3459817</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3459817</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3161914</t>
+          <t>3173391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3824700</t>
+          <t>3811887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/SE_ADU-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Habitat-trans_orig.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654258</t>
+          <t>653331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>726255</t>
+          <t>725058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656108</t>
+          <t>657305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728105</t>
+          <t>729032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>923443</t>
+          <t>925452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1015366</t>
+          <t>1014505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914827</t>
+          <t>915688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1006750</t>
+          <t>1004741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646587</t>
+          <t>646368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721453</t>
+          <t>722505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640897</t>
+          <t>639845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>715763</t>
+          <t>715982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>994046</t>
+          <t>997178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1085351</t>
+          <t>1081659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>895483</t>
+          <t>899175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>986788</t>
+          <t>983656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3299502</t>
+          <t>3291559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3461675</t>
+          <t>3465110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3194066</t>
+          <t>3190631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3356239</t>
+          <t>3364182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>657282</t>
+          <t>661931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>739166</t>
+          <t>735819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661353</t>
+          <t>664700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743237</t>
+          <t>738588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>989133</t>
+          <t>987730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1083532</t>
+          <t>1079810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966599</t>
+          <t>970321</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1060998</t>
+          <t>1062401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>733424</t>
+          <t>734601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>814803</t>
+          <t>816984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>719994</t>
+          <t>717813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>801373</t>
+          <t>800196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1010904</t>
+          <t>1006498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1099632</t>
+          <t>1093996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>900008</t>
+          <t>905644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>988736</t>
+          <t>993142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3473059</t>
+          <t>3474644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3648696</t>
+          <t>3647065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3336392</t>
+          <t>3338023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3512029</t>
+          <t>3510444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>636149</t>
+          <t>634377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>709472</t>
+          <t>707825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>638167</t>
+          <t>639814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711490</t>
+          <t>713262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>998409</t>
+          <t>996230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1089587</t>
+          <t>1090491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975757</t>
+          <t>974853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1066935</t>
+          <t>1069114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>742476</t>
+          <t>743984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824479</t>
+          <t>826557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>720084</t>
+          <t>718006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>802087</t>
+          <t>800579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>999795</t>
+          <t>997485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1088710</t>
+          <t>1087217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>892636</t>
+          <t>894129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>981551</t>
+          <t>983861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3459508</t>
+          <t>3458868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3628134</t>
+          <t>3624708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3310758</t>
+          <t>3314184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3479384</t>
+          <t>3480024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>725331</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>681343</t>
+          <t>697852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>811367</t>
+          <t>772032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690709</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549405</t>
+          <t>652857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>679429</t>
+          <t>727037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>958652</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649535</t>
+          <t>1023665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1097923</t>
+          <t>1119163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>52,78%</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1053593</t>
+          <t>1001228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1501981</t>
+          <t>1096726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>814492</t>
+          <t>766754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1156841</t>
+          <t>852205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>481205</t>
+          <t>763127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823554</t>
+          <t>848578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119042</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1039486</t>
+          <t>1075328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1207217</t>
+          <t>1163586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814546</t>
+          <t>945518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>982277</t>
+          <t>1033776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3360210</t>
+          <t>3647018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3998706</t>
+          <t>3820432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3173391</t>
+          <t>3449284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3811887</t>
+          <t>3622698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
